--- a/results/model_comparison/future_model_comparison.xlsx
+++ b/results/model_comparison/future_model_comparison.xlsx
@@ -467,7 +467,7 @@
         <v>0.6773923298243364</v>
       </c>
       <c r="F2" t="n">
-        <v>6.069548845291138</v>
+        <v>3.884172677993774</v>
       </c>
     </row>
     <row r="3">
@@ -489,7 +489,7 @@
         <v>0.6625538587120184</v>
       </c>
       <c r="F3" t="n">
-        <v>45.74005603790283</v>
+        <v>40.26173973083496</v>
       </c>
     </row>
     <row r="4">
@@ -511,7 +511,7 @@
         <v>0.5746229766000925</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3123624324798584</v>
+        <v>0.2856137752532959</v>
       </c>
     </row>
   </sheetData>
